--- a/rcads/data/xls/30_Codebooks.xlsx
+++ b/rcads/data/xls/30_Codebooks.xlsx
@@ -10,7 +10,7 @@
     <sheet sheetId="1" r:id="rId1" name="_30_Codebooks"/>
   </sheets>
   <definedNames>
-    <definedName name="_30_Codebooks">'_30_Codebooks'!$A$1:$D$44</definedName>
+    <definedName name="_30_Codebooks">'_30_Codebooks'!$A$1:$D$49</definedName>
   </definedNames>
   <calcPr calcId="125725" fullCalcOnLoad="true"/>
 </workbook>
@@ -343,7 +343,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D44"/>
+  <dimension ref="A1:D49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row outlineLevel="0" r="1">
@@ -1056,6 +1056,86 @@
         <v>29</v>
       </c>
     </row>
+    <row outlineLevel="0" r="45">
+      <c r="A45" s="0">
+        <v>44</v>
+      </c>
+      <c r="B45" s="0" t="inlineStr">
+        <is>
+          <t>4.0-item-Frequency-Chinese (Traditional)</t>
+        </is>
+      </c>
+      <c r="C45" s="0">
+        <v>1</v>
+      </c>
+      <c r="D45" s="0">
+        <v>25</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="46">
+      <c r="A46" s="0">
+        <v>45</v>
+      </c>
+      <c r="B46" s="0" t="inlineStr">
+        <is>
+          <t>4.0-item-Frequency-Malay</t>
+        </is>
+      </c>
+      <c r="C46" s="0">
+        <v>1</v>
+      </c>
+      <c r="D46" s="0">
+        <v>28</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="47">
+      <c r="A47" s="0">
+        <v>46</v>
+      </c>
+      <c r="B47" s="0" t="inlineStr">
+        <is>
+          <t>4.0-item-Frequency-Albanian</t>
+        </is>
+      </c>
+      <c r="C47" s="0">
+        <v>1</v>
+      </c>
+      <c r="D47" s="0">
+        <v>42</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="48">
+      <c r="A48" s="0">
+        <v>47</v>
+      </c>
+      <c r="B48" s="0" t="inlineStr">
+        <is>
+          <t>4.3-item-Frequency-English</t>
+        </is>
+      </c>
+      <c r="C48" s="0">
+        <v>1</v>
+      </c>
+      <c r="D48" s="0">
+        <v>1</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="49">
+      <c r="A49" s="0">
+        <v>48</v>
+      </c>
+      <c r="B49" s="0" t="inlineStr">
+        <is>
+          <t>4.1-item-Frequency-French</t>
+        </is>
+      </c>
+      <c r="C49" s="0">
+        <v>1</v>
+      </c>
+      <c r="D49" s="0">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
